--- a/filename.xlsx
+++ b/filename.xlsx
@@ -467,10 +467,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A2" t="n">
+        <v>10</v>
       </c>
       <c r="B2" t="n">
         <v>3</v>
@@ -500,10 +498,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A3" t="n">
+        <v>10</v>
       </c>
       <c r="B3" t="n">
         <v>3</v>
@@ -529,10 +525,8 @@
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A4" t="n">
+        <v>11</v>
       </c>
       <c r="B4" t="n">
         <v>5</v>
@@ -562,10 +556,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A5" t="n">
+        <v>10</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
@@ -591,10 +583,8 @@
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A6" t="n">
+        <v>10</v>
       </c>
       <c r="B6" t="n">
         <v>3</v>
@@ -620,10 +610,8 @@
       <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A7" t="n">
+        <v>10</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -649,10 +637,8 @@
       <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A8" t="n">
+        <v>9</v>
       </c>
       <c r="B8" t="n">
         <v>3</v>
@@ -682,10 +668,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A9" t="n">
+        <v>10</v>
       </c>
       <c r="B9" t="n">
         <v>4</v>
@@ -715,10 +699,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A10" t="n">
+        <v>10</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
@@ -744,10 +726,8 @@
       <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A11" t="n">
+        <v>12</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
@@ -777,10 +757,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A12" t="n">
+        <v>12</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -806,10 +784,8 @@
       <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A13" t="n">
+        <v>11</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
@@ -835,10 +811,8 @@
       <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A14" t="n">
+        <v>12</v>
       </c>
       <c r="B14" t="n">
         <v>2</v>
@@ -864,10 +838,8 @@
       <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A15" t="n">
+        <v>11</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
@@ -893,10 +865,8 @@
       <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A16" t="n">
+        <v>9</v>
       </c>
       <c r="B16" t="n">
         <v>5</v>
@@ -926,10 +896,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A17" t="n">
+        <v>9</v>
       </c>
       <c r="B17" t="n">
         <v>3</v>
@@ -955,10 +923,8 @@
       <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A18" t="n">
+        <v>10</v>
       </c>
       <c r="B18" t="n">
         <v>2</v>
@@ -988,10 +954,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" t="n">
         <v>4</v>
@@ -1017,10 +981,8 @@
       <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A20" t="n">
+        <v>11</v>
       </c>
       <c r="B20" t="n">
         <v>4</v>
@@ -1046,10 +1008,8 @@
       <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A21" t="n">
+        <v>11</v>
       </c>
       <c r="B21" t="n">
         <v>4</v>
@@ -1079,10 +1039,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A22" t="n">
+        <v>10</v>
       </c>
       <c r="B22" t="n">
         <v>4</v>
@@ -1112,10 +1070,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A23" t="n">
+        <v>10</v>
       </c>
       <c r="B23" t="n">
         <v>2</v>
@@ -1141,10 +1097,8 @@
       <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A24" t="n">
+        <v>12</v>
       </c>
       <c r="B24" t="n">
         <v>3</v>
@@ -1170,10 +1124,8 @@
       <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A25" t="n">
+        <v>12</v>
       </c>
       <c r="B25" t="n">
         <v>3</v>
@@ -1199,10 +1151,8 @@
       <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A26" t="n">
+        <v>9</v>
       </c>
       <c r="B26" t="n">
         <v>2</v>
@@ -1228,10 +1178,8 @@
       <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A27" t="n">
+        <v>10</v>
       </c>
       <c r="B27" t="n">
         <v>2</v>
@@ -1257,10 +1205,8 @@
       <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A28" t="n">
+        <v>11</v>
       </c>
       <c r="B28" t="n">
         <v>4</v>
@@ -1286,10 +1232,8 @@
       <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A29" t="n">
+        <v>12</v>
       </c>
       <c r="B29" t="n">
         <v>3</v>
@@ -1315,10 +1259,8 @@
       <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A30" t="n">
+        <v>10</v>
       </c>
       <c r="B30" t="n">
         <v>3</v>
@@ -1344,10 +1286,8 @@
       <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A31" t="n">
+        <v>10</v>
       </c>
       <c r="B31" t="n">
         <v>2</v>
@@ -1373,10 +1313,8 @@
       <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A32" t="n">
+        <v>8</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
@@ -1402,10 +1340,8 @@
       <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A33" t="n">
+        <v>8</v>
       </c>
       <c r="B33" t="n">
         <v>3</v>
@@ -1431,10 +1367,8 @@
       <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A34" t="n">
+        <v>8</v>
       </c>
       <c r="B34" t="n">
         <v>3</v>
@@ -1460,10 +1394,8 @@
       <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A35" t="n">
+        <v>8</v>
       </c>
       <c r="B35" t="n">
         <v>5</v>
@@ -1489,10 +1421,8 @@
       <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A36" t="n">
+        <v>10</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
@@ -1518,10 +1448,8 @@
       <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A37" t="n">
+        <v>11</v>
       </c>
       <c r="B37" t="n">
         <v>2</v>
@@ -1551,10 +1479,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A38" t="n">
+        <v>10</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
@@ -1584,10 +1510,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A39" t="n">
+        <v>11</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
@@ -1617,10 +1541,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A40" t="n">
+        <v>11</v>
       </c>
       <c r="B40" t="n">
         <v>4</v>
@@ -1646,10 +1568,8 @@
       <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A41" t="n">
+        <v>11</v>
       </c>
       <c r="B41" t="n">
         <v>4</v>
@@ -1675,10 +1595,8 @@
       <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A42" t="n">
+        <v>11</v>
       </c>
       <c r="B42" t="n">
         <v>5</v>
@@ -1704,10 +1622,8 @@
       <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A43" t="n">
+        <v>9</v>
       </c>
       <c r="B43" t="n">
         <v>4</v>
@@ -1733,10 +1649,8 @@
       <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A44" t="n">
+        <v>9</v>
       </c>
       <c r="B44" t="n">
         <v>3</v>
@@ -1762,10 +1676,8 @@
       <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A45" t="n">
+        <v>12</v>
       </c>
       <c r="B45" t="n">
         <v>5</v>
@@ -1791,10 +1703,8 @@
       <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A46" t="n">
+        <v>11</v>
       </c>
       <c r="B46" t="n">
         <v>3</v>
@@ -1824,10 +1734,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A47" t="n">
+        <v>10</v>
       </c>
       <c r="B47" t="n">
         <v>4</v>
@@ -1857,10 +1765,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A48" t="n">
+        <v>11</v>
       </c>
       <c r="B48" t="n">
         <v>3</v>
@@ -1886,10 +1792,8 @@
       <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A49" t="n">
+        <v>11</v>
       </c>
       <c r="B49" t="n">
         <v>3</v>
@@ -1919,10 +1823,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A50" t="n">
+        <v>9</v>
       </c>
       <c r="B50" t="n">
         <v>3</v>
@@ -1952,10 +1854,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A51" t="n">
+        <v>8</v>
       </c>
       <c r="B51" t="n">
         <v>3</v>
@@ -1985,10 +1885,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A52" t="n">
+        <v>8</v>
       </c>
       <c r="B52" t="n">
         <v>4</v>
@@ -2018,10 +1916,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A53" t="n">
+        <v>10</v>
       </c>
       <c r="B53" t="n">
         <v>4</v>
@@ -2047,10 +1943,8 @@
       <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A54" t="n">
+        <v>9</v>
       </c>
       <c r="B54" t="n">
         <v>4</v>
@@ -2080,10 +1974,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A55" t="n">
+        <v>9</v>
       </c>
       <c r="B55" t="n">
         <v>2</v>
@@ -2109,10 +2001,8 @@
       <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A56" t="n">
+        <v>11</v>
       </c>
       <c r="B56" t="n">
         <v>4</v>
@@ -2138,10 +2028,8 @@
       <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A57" t="n">
+        <v>12</v>
       </c>
       <c r="B57" t="n">
         <v>3</v>
@@ -2167,10 +2055,8 @@
       <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A58" t="n">
+        <v>12</v>
       </c>
       <c r="B58" t="n">
         <v>2</v>
@@ -2196,10 +2082,8 @@
       <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A59" t="n">
+        <v>9</v>
       </c>
       <c r="B59" t="n">
         <v>2</v>
@@ -2225,10 +2109,8 @@
       <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A60" t="n">
+        <v>9</v>
       </c>
       <c r="B60" t="n">
         <v>4</v>
@@ -2254,10 +2136,8 @@
       <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A61" t="n">
+        <v>8</v>
       </c>
       <c r="B61" t="n">
         <v>3</v>
@@ -2287,10 +2167,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A62" t="n">
+        <v>8</v>
       </c>
       <c r="B62" t="n">
         <v>3</v>
@@ -2316,10 +2194,8 @@
       <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A63" t="n">
+        <v>8</v>
       </c>
       <c r="B63" t="n">
         <v>4</v>
@@ -2349,10 +2225,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A64" t="n">
+        <v>8</v>
       </c>
       <c r="B64" t="n">
         <v>4</v>
@@ -2378,10 +2252,8 @@
       <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A65" t="n">
+        <v>9</v>
       </c>
       <c r="B65" t="n">
         <v>1</v>
@@ -2411,10 +2283,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A66" t="n">
+        <v>8</v>
       </c>
       <c r="B66" t="n">
         <v>3</v>
@@ -2444,10 +2314,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A67" t="n">
+        <v>10</v>
       </c>
       <c r="B67" t="n">
         <v>3</v>
@@ -2473,10 +2341,8 @@
       <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A68" t="n">
+        <v>8</v>
       </c>
       <c r="B68" t="n">
         <v>4</v>
@@ -2506,10 +2372,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A69" t="n">
+        <v>8</v>
       </c>
       <c r="B69" t="n">
         <v>5</v>
@@ -2539,10 +2403,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A70" t="n">
+        <v>8</v>
       </c>
       <c r="B70" t="n">
         <v>4</v>
@@ -2572,10 +2434,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A71" t="n">
+        <v>10</v>
       </c>
       <c r="B71" t="n">
         <v>2</v>
@@ -2605,10 +2465,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A72" t="n">
+        <v>11</v>
       </c>
       <c r="B72" t="n">
         <v>4</v>
@@ -2634,10 +2492,8 @@
       <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A73" t="n">
+        <v>11</v>
       </c>
       <c r="B73" t="n">
         <v>1</v>
@@ -2663,10 +2519,8 @@
       <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A74" t="n">
+        <v>8</v>
       </c>
       <c r="B74" t="n">
         <v>2</v>
@@ -2697,10 +2551,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A75" t="n">
+        <v>8</v>
       </c>
       <c r="B75" t="n">
         <v>2</v>
@@ -2730,10 +2582,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A76" t="n">
+        <v>9</v>
       </c>
       <c r="B76" t="n">
         <v>4</v>
@@ -2763,10 +2613,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A77" t="n">
+        <v>10</v>
       </c>
       <c r="B77" t="n">
         <v>1</v>
@@ -2792,10 +2640,8 @@
       <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A78" t="n">
+        <v>10</v>
       </c>
       <c r="B78" t="n">
         <v>5</v>
@@ -2821,10 +2667,8 @@
       <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A79" t="n">
+        <v>10</v>
       </c>
       <c r="B79" t="n">
         <v>3</v>
@@ -2854,10 +2698,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A80" t="n">
+        <v>8</v>
       </c>
       <c r="B80" t="n">
         <v>5</v>
@@ -2887,10 +2729,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A81" t="n">
+        <v>8</v>
       </c>
       <c r="B81" t="n">
         <v>5</v>
@@ -2920,10 +2760,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A82" t="n">
+        <v>8</v>
       </c>
       <c r="B82" t="n">
         <v>3</v>
@@ -2953,10 +2791,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A83" t="n">
+        <v>8</v>
       </c>
       <c r="B83" t="n">
         <v>5</v>
@@ -2982,10 +2818,8 @@
       <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A84" t="n">
+        <v>8</v>
       </c>
       <c r="B84" t="n">
         <v>2</v>
@@ -3011,10 +2845,8 @@
       <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A85" t="n">
+        <v>9</v>
       </c>
       <c r="B85" t="n">
         <v>1</v>
@@ -3044,10 +2876,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A86" t="n">
+        <v>9</v>
       </c>
       <c r="B86" t="n">
         <v>2</v>
@@ -3073,10 +2903,8 @@
       <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A87" t="n">
+        <v>10</v>
       </c>
       <c r="B87" t="n">
         <v>2</v>
@@ -3102,10 +2930,8 @@
       <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A88" t="n">
+        <v>11</v>
       </c>
       <c r="B88" t="n">
         <v>3</v>
@@ -3131,10 +2957,8 @@
       <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A89" t="n">
+        <v>10</v>
       </c>
       <c r="B89" t="n">
         <v>5</v>
@@ -3164,10 +2988,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A90" t="n">
+        <v>12</v>
       </c>
       <c r="B90" t="n">
         <v>2</v>
@@ -3197,10 +3019,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A91" t="n">
+        <v>9</v>
       </c>
       <c r="B91" t="n">
         <v>2</v>
@@ -3226,10 +3046,8 @@
       <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A92" t="n">
+        <v>9</v>
       </c>
       <c r="B92" t="n">
         <v>5</v>
@@ -3259,10 +3077,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A93" t="n">
+        <v>9</v>
       </c>
       <c r="B93" t="n">
         <v>4</v>
@@ -3288,10 +3104,8 @@
       <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A94" t="n">
+        <v>9</v>
       </c>
       <c r="B94" t="n">
         <v>2</v>
@@ -3321,10 +3135,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A95" t="n">
+        <v>8</v>
       </c>
       <c r="B95" t="n">
         <v>5</v>

--- a/filename.xlsx
+++ b/filename.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1511,61 +1511,61 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['After school']</t>
+          <t>['During Flex time', 'After school']</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>['To ask questions']</t>
+          <t>['To do homework', 'To work on other projects']</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lack of energy or motivation</t>
+          <t>Distractions in class. i.e. devices/people talking</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>please don’t remove flex because i already cannot get to school on time as it is.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>11</v>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['During Flex time']</t>
+          <t>['After school']</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>['To study or ask for help']</t>
+          <t>['To ask questions']</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nothing prevents me from using flex time</t>
+          <t>Lack of energy or motivation</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>please don’t remove flex because i already cannot get to school on time as it is.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1576,21 +1576,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>["I don't come in for help"]</t>
+          <t>['During Flex time']</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>['To work on other projects', 'To meet with peers', 'To do homework']</t>
+          <t>['To study or ask for help']</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Communicating with peers</t>
+          <t>Nothing prevents me from using flex time</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr"/>
     </row>
@@ -1599,52 +1599,52 @@
         <v>11</v>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>['During Flex time']</t>
+          <t>["I don't come in for help"]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>['To do homework', 'To study or ask for help', 'To ask questions', 'To meet with peers', 'To work on other projects']</t>
+          <t>['To work on other projects', 'To meet with peers', 'To do homework']</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lack of energy or motivation</t>
+          <t>Communicating with peers</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>['During Flex time', 'Lunch']</t>
+          <t>['During Flex time']</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>['To ask questions', 'To study or ask for help']</t>
+          <t>['To do homework', 'To study or ask for help', 'To ask questions', 'To meet with peers', 'To work on other projects']</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Availability of teachers</t>
+          <t>Lack of energy or motivation</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="inlineStr"/>
     </row>
@@ -1653,16 +1653,16 @@
         <v>9</v>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>['During Flex time']</t>
+          <t>['During Flex time', 'Lunch']</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>['To meet with peers']</t>
+          <t>['To ask questions', 'To study or ask for help']</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1677,24 +1677,24 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>['During Flex time', 'After school', 'Lunch']</t>
+          <t>['During Flex time']</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>['To study or ask for help', 'To ask questions', 'To do homework']</t>
+          <t>['To meet with peers']</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nothing prevents me from using flex time</t>
+          <t>Availability of teachers</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1704,19 +1704,19 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>['During Flex time']</t>
+          <t>['During Flex time', 'After school', 'Lunch']</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>['To study or ask for help', 'To do homework']</t>
+          <t>['To study or ask for help', 'To ask questions', 'To do homework']</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1725,20 +1725,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Flex time a great way to catch up, ask questions, and support yourself as well as others. The only downside to flex time is that it is in the morning where most people are tired.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1747,7 +1743,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>['To do homework', 'To study or ask for help', 'To ask questions']</t>
+          <t>['To study or ask for help', 'To do homework']</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1760,16 +1756,16 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Flex time has been invaluable to me as a student. I would not be where I currently am if I was not able to utilize flex time to improve my academics.</t>
+          <t>Flex time a great way to catch up, ask questions, and support yourself as well as others. The only downside to flex time is that it is in the morning where most people are tired.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1778,7 +1774,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>['To study or ask for help']</t>
+          <t>['To do homework', 'To study or ask for help', 'To ask questions']</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1787,9 +1783,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>7</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Flex time has been invaluable to me as a student. I would not be where I currently am if I was not able to utilize flex time to improve my academics.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>['To do homework', 'To work on other projects', 'To study or ask for help', 'To meet with peers']</t>
+          <t>['To study or ask for help']</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1814,17 +1814,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>DON'T REMOVE IT!!!!!!!!!!!!</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B50" t="n">
         <v>3</v>
@@ -1836,7 +1832,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>['To study or ask for help', 'To ask questions', 'To do homework']</t>
+          <t>['To do homework', 'To work on other projects', 'To study or ask for help', 'To meet with peers']</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1845,17 +1841,17 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>flex time is really helpful when ive missed a day and need time to catchup on notes.</t>
+          <t>DON'T REMOVE IT!!!!!!!!!!!!</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B51" t="n">
         <v>3</v>
@@ -1867,20 +1863,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>['To study or ask for help']</t>
+          <t>['To study or ask for help', 'To ask questions', 'To do homework']</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lack of energy or motivation</t>
+          <t>Nothing prevents me from using flex time</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">No sorry </t>
+          <t>flex time is really helpful when ive missed a day and need time to catchup on notes.</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1885,7 @@
         <v>8</v>
       </c>
       <c r="B52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1903,21 +1899,21 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nothing prevents me from using flex time</t>
+          <t>Lack of energy or motivation</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t xml:space="preserve">No sorry </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B53" t="n">
         <v>4</v>
@@ -1929,22 +1925,26 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>['To do homework', 'To work on other projects', 'To meet with peers']</t>
+          <t>['To study or ask for help']</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lack of energy or motivation</t>
+          <t>Nothing prevents me from using flex time</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>3</v>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B54" t="n">
         <v>4</v>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>['To do homework', 'To study or ask for help', 'To meet with peers', 'To work on other projects']</t>
+          <t>['To do homework', 'To work on other projects', 'To meet with peers']</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1965,29 +1965,25 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>don't remove flex time 😓</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>9</v>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>['During Flex time', "I don't come in for help"]</t>
+          <t>['During Flex time']</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>['To study or ask for help']</t>
+          <t>['To do homework', 'To study or ask for help', 'To meet with peers', 'To work on other projects']</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1996,43 +1992,47 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>8</v>
-      </c>
-      <c r="G55" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>don't remove flex time 😓</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>['During Flex time']</t>
+          <t>['During Flex time', "I don't come in for help"]</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>['To do homework']</t>
+          <t>['To study or ask for help']</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nothing prevents me from using flex time</t>
+          <t>Lack of energy or motivation</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2041,16 +2041,16 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>['To study or ask for help', 'To do homework']</t>
+          <t>['To do homework']</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lack of energy or motivation</t>
+          <t>Nothing prevents me from using flex time</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G57" t="inlineStr"/>
     </row>
@@ -2059,16 +2059,16 @@
         <v>12</v>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>["I don't come in for help"]</t>
+          <t>['During Flex time']</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>['To work on other projects']</t>
+          <t>['To study or ask for help', 'To do homework']</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2077,34 +2077,34 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B59" t="n">
         <v>2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>['During Flex time']</t>
+          <t>["I don't come in for help"]</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>['To do homework', 'To study or ask for help', 'To ask questions']</t>
+          <t>['To work on other projects']</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Communicating with peers</t>
+          <t>Lack of energy or motivation</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G59" t="inlineStr"/>
     </row>
@@ -2113,21 +2113,21 @@
         <v>9</v>
       </c>
       <c r="B60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>['During Flex time', 'Lunch']</t>
+          <t>['During Flex time']</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>['To study or ask for help', 'To ask questions', 'To do homework', 'To meet with peers', 'To work on other projects']</t>
+          <t>['To do homework', 'To study or ask for help', 'To ask questions']</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nothing prevents me from using flex time</t>
+          <t>Communicating with peers</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2137,34 +2137,30 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>['During Flex time']</t>
+          <t>['During Flex time', 'Lunch']</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>['To do homework']</t>
+          <t>['To study or ask for help', 'To ask questions', 'To do homework', 'To meet with peers', 'To work on other projects']</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lack of energy or motivation</t>
+          <t>Nothing prevents me from using flex time</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2180,7 +2176,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>['To ask questions', 'To meet with peers', 'To do homework']</t>
+          <t>['To do homework']</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2189,16 +2185,20 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>5</v>
-      </c>
-      <c r="G62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>8</v>
       </c>
       <c r="B63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2207,22 +2207,18 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>['To do homework', 'To study or ask for help']</t>
+          <t>['To ask questions', 'To meet with peers', 'To do homework']</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nothing prevents me from using flex time</t>
+          <t>Lack of energy or motivation</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2238,7 +2234,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>['To ask questions', 'To study or ask for help']</t>
+          <t>['To do homework', 'To study or ask for help']</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2249,112 +2245,112 @@
       <c r="F64" t="n">
         <v>1</v>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>['During Flex time']</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>['To ask questions', 'To study or ask for help']</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Nothing prevents me from using flex time</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
         <v>1</v>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>["I don't come in for help"]</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>['To work on other projects']</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Nothing prevents me from using flex time</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>5</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>It doesn’t effect to me if flex time removed. I just spend my time in library ı don’ use flex.</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>8</v>
       </c>
       <c r="B66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>['Lunch', "I don't come in for help", 'During Flex time']</t>
+          <t>["I don't come in for help", 'During Flex time']</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>['To meet with peers', 'To ask questions', 'To work on other projects']</t>
+          <t>['To meet with peers', 'To ask questions']</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nothing prevents me from using flex time</t>
+          <t>Distractions in class. i.e. devices/people talking</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>4</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I think flex is a really good block for asking teachers about work or just to do some work for example like me I’m in 8th grade and it’s a big change from elementary to high school so I sometimes use flex to ask my teacher about things that I’m still trying to adapt and flex is also fun because I can sometimes meet with peers which we don’t have classes together and just chat </t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>['During Flex time']</t>
+          <t>["I don't come in for help"]</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>['To study or ask for help']</t>
+          <t>['To work on other projects']</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lack of energy or motivation</t>
+          <t>Nothing prevents me from using flex time</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>4</v>
-      </c>
-      <c r="G67" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>It doesn’t effect to me if flex time removed. I just spend my time in library ı don’ use flex.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>8</v>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>["I don't come in for help"]</t>
+          <t>['Lunch', "I don't come in for help", 'During Flex time']</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>['To do homework', 'To work on other projects']</t>
+          <t>['To meet with peers', 'To ask questions', 'To work on other projects']</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2363,20 +2359,20 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>no</t>
+          <t xml:space="preserve">I think flex is a really good block for asking teachers about work or just to do some work for example like me I’m in 8th grade and it’s a big change from elementary to high school so I sometimes use flex to ask my teacher about things that I’m still trying to adapt and flex is also fun because I can sometimes meet with peers which we don’t have classes together and just chat </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -2385,22 +2381,18 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>['To study or ask for help', 'To ask questions']</t>
+          <t>['To study or ask for help']</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nothing prevents me from using flex time</t>
+          <t>Lack of energy or motivation</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>I believe flex time is a useful addition to the school schedule, and should be removed due to a few people not using it the way its intended. Many students like myself find it an efficient time to ask our teachers questions or for assistance with assignments. If flex would be taken away, we would have to find another time during school hours to discuss our questions, and most students have other activities or responsibilities during breaks and such. This means they'd be unable to improve their understandings of the subject they have questions about. Please don't remove flex time😭😭😭 a lot of people use it effectively and efficiently!!!</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2411,12 +2403,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>['Lunch', 'During Flex time']</t>
+          <t>["I don't come in for help"]</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>['To study or ask for help', 'To ask questions']</t>
+          <t>['To do homework', 'To work on other projects']</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2429,16 +2421,16 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Having flex is very useful, please don’t take it away.</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -2447,38 +2439,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>['To work on other projects', 'To study or ask for help', 'To do homework']</t>
+          <t>['To study or ask for help', 'To ask questions']</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lack of energy or motivation</t>
+          <t>Nothing prevents me from using flex time</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>I believe flex time is a useful addition to the school schedule, and should be removed due to a few people not using it the way its intended. Many students like myself find it an efficient time to ask our teachers questions or for assistance with assignments. If flex would be taken away, we would have to find another time during school hours to discuss our questions, and most students have other activities or responsibilities during breaks and such. This means they'd be unable to improve their understandings of the subject they have questions about. Please don't remove flex time😭😭😭 a lot of people use it effectively and efficiently!!!</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B72" t="n">
         <v>4</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>['During Flex time']</t>
+          <t>['Lunch', 'During Flex time']</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>['To do homework', 'To study or ask for help', 'To ask questions', 'To work on other projects']</t>
+          <t>['To study or ask for help', 'To ask questions']</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2487,25 +2479,29 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
-      </c>
-      <c r="G72" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Having flex is very useful, please don’t take it away.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>['After school']</t>
+          <t>['During Flex time']</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>['To meet with peers']</t>
+          <t>['To work on other projects', 'To study or ask for help', 'To do homework']</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2514,137 +2510,137 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>4</v>
-      </c>
-      <c r="G73" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
+        <v>11</v>
+      </c>
+      <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>['During Flex time']</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>['To do homework', 'To study or ask for help', 'To ask questions', 'To work on other projects']</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Nothing prevents me from using flex time</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>11</v>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>['After school']</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>['To meet with peers']</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Lack of energy or motivation</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>4</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
         <v>8</v>
       </c>
-      <c r="B74" t="n">
-        <v>2</v>
-      </c>
-      <c r="C74" t="inlineStr">
+      <c r="B76" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" t="inlineStr">
         <is>
           <t>['Lunch']</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>['To work on other projects', 'To meet with peers', 'To ask questions', 'To study or ask for help', 'To do homework']</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Nothing prevents me from using flex time</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Nothing prevents me from using flex time</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>If flex time was removed then it would become more troubling for teachers as those who have unfinished homework(not me) will come to class with undone homework or push teachers to stay later afterschool to help. The reason people come to flex with homework Is because they may have a lot going on at home And they find it difficult to focus so they bring their homework to school just in time to finish it by deadline. If this were removed, Not very many students would excel and fall behind, and you adults will complain about our generation being Lazy, unproductive, lousy, unuseful, and stupid. Although I’m not accusing anybody of anything, I’m taking the survey as my expression and opinion of this topic. If anything, I strongly believe that flex should be extended every day rather than removed. Sincerely,
 – ROHAN Sharma</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>8</v>
-      </c>
-      <c r="B75" t="n">
-        <v>2</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>['During Flex time']</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>['To meet with peers']</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Communicating with peers</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>3</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>9</v>
-      </c>
-      <c r="B76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>['During Flex time']</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>['To study or ask for help', 'To ask questions']</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Nothing prevents me from using flex time</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>["I don't come in for help"]</t>
+          <t>['During Flex time']</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>['To ask questions']</t>
+          <t>['To meet with peers']</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Availability of teachers</t>
+          <t>Communicating with peers</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -2653,7 +2649,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>['To do homework', 'To work on other projects']</t>
+          <t>['To study or ask for help', 'To ask questions']</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2662,44 +2658,44 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
         <v>10</v>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>['During Flex time']</t>
+          <t>["I don't come in for help"]</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>['To study or ask for help']</t>
+          <t>['To ask questions']</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lack of energy or motivation</t>
+          <t>Availability of teachers</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B80" t="n">
         <v>5</v>
@@ -2711,29 +2707,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>['To do homework', 'To study or ask for help', 'To ask questions', 'To meet with peers', 'To work on other projects']</t>
+          <t>['To do homework', 'To work on other projects']</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Lack of energy or motivation</t>
+          <t>Nothing prevents me from using flex time</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I love flex </t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -2742,7 +2734,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>['To do homework', 'To study or ask for help', 'To work on other projects', 'To meet with peers']</t>
+          <t>['To study or ask for help']</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2755,7 +2747,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>KEEP FLEX I WANT MY LIBRARY TIME</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2764,16 +2756,16 @@
         <v>8</v>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>['During Flex time', 'After school']</t>
+          <t>['During Flex time']</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>['To do homework', 'To study or ask for help', 'To meet with peers', 'To work on other projects']</t>
+          <t>['To do homework', 'To study or ask for help', 'To ask questions', 'To meet with peers', 'To work on other projects']</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2786,7 +2778,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pls dont remove flex time i dont want school to start at 8:20 i love the free breakfast club</t>
+          <t xml:space="preserve">I love flex </t>
         </is>
       </c>
     </row>
@@ -2804,34 +2796,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>['To do homework', 'To study or ask for help', 'To ask questions', 'To work on other projects']</t>
+          <t>['To do homework', 'To study or ask for help', 'To work on other projects', 'To meet with peers']</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nothing prevents me from using flex time</t>
+          <t>Lack of energy or motivation</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>KEEP FLEX I WANT MY LIBRARY TIME</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
         <v>8</v>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>["I don't come in for help"]</t>
+          <t>['During Flex time', 'After school']</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>['To meet with peers']</t>
+          <t>['To do homework', 'To study or ask for help', 'To meet with peers', 'To work on other projects']</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2842,54 +2838,54 @@
       <c r="F84" t="n">
         <v>0</v>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Pls dont remove flex time i dont want school to start at 8:20 i love the free breakfast club</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>["I don't come in for help"]</t>
+          <t>['During Flex time']</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>['To ask questions']</t>
+          <t>['To do homework', 'To study or ask for help', 'To ask questions', 'To work on other projects']</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lack of energy or motivation</t>
+          <t>Nothing prevents me from using flex time</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>5</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B86" t="n">
         <v>2</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>['During Flex time']</t>
+          <t>["I don't come in for help"]</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>['To work on other projects']</t>
+          <t>['To meet with peers']</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2898,25 +2894,25 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>['Lunch', 'During Flex time']</t>
+          <t>["I don't come in for help"]</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>['To do homework']</t>
+          <t>['To ask questions']</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2925,16 +2921,20 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>['To do homework', 'To study or ask for help', 'To ask questions']</t>
+          <t>['To work on other projects']</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr"/>
     </row>
@@ -2961,47 +2961,43 @@
         <v>10</v>
       </c>
       <c r="B89" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>['During Flex time']</t>
+          <t>['Lunch', 'During Flex time']</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>['To study or ask for help', 'To ask questions', 'To do homework']</t>
+          <t>['To do homework']</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nothing prevents me from using flex time</t>
+          <t>Lack of energy or motivation</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I still want to have Flex Time to be able able to ask my teacher when I cannot do the assignment </t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>['After school', 'Lunch']</t>
+          <t>['During Flex time']</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>['To meet with peers', 'To work on other projects', 'To study or ask for help']</t>
+          <t>['To do homework', 'To study or ask for help', 'To ask questions']</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3010,20 +3006,16 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>7</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -3032,7 +3024,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>['To meet with peers']</t>
+          <t>['To study or ask for help', 'To ask questions', 'To do homework']</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3041,38 +3033,42 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
-      </c>
-      <c r="G91" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I still want to have Flex Time to be able able to ask my teacher when I cannot do the assignment </t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B92" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>['During Flex time']</t>
+          <t>['After school', 'Lunch']</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>['To study or ask for help', 'To meet with peers', 'To work on other projects', 'To ask questions']</t>
+          <t>['To meet with peers', 'To work on other projects', 'To study or ask for help']</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Availability of teachers</t>
+          <t>Lack of energy or motivation</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pls don't remove flex</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3077,7 @@
         <v>9</v>
       </c>
       <c r="B93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -3090,16 +3086,16 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>['To do homework', 'To study or ask for help', 'To ask questions', 'To work on other projects', 'To meet with peers']</t>
+          <t>['To meet with peers']</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Lack of energy or motivation</t>
+          <t>Nothing prevents me from using flex time</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G93" t="inlineStr"/>
     </row>
@@ -3108,58 +3104,116 @@
         <v>9</v>
       </c>
       <c r="B94" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>['Lunch', 'After school']</t>
+          <t>['During Flex time']</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>['To ask questions']</t>
+          <t>['To study or ask for help', 'To meet with peers', 'To work on other projects', 'To ask questions']</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lack of energy or motivation</t>
+          <t>Availability of teachers</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I don’t usually go to flex, but it’s always good to have a time for me to get some extra help</t>
+          <t>Pls don't remove flex</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
+        <v>9</v>
+      </c>
+      <c r="B95" t="n">
+        <v>4</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>['During Flex time']</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>['To do homework', 'To study or ask for help', 'To ask questions', 'To work on other projects', 'To meet with peers']</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Lack of energy or motivation</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>9</v>
+      </c>
+      <c r="B96" t="n">
+        <v>2</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>['Lunch', 'After school']</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>['To ask questions']</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Lack of energy or motivation</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>2</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>I don’t usually go to flex, but it’s always good to have a time for me to get some extra help</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
         <v>8</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B97" t="n">
         <v>5</v>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>['During Flex time', 'After school']</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>['To do homework', 'To study or ask for help', 'To ask questions', 'To work on other projects']</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>Availability of teachers</t>
         </is>
       </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/filename.xlsx
+++ b/filename.xlsx
@@ -456,8 +456,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">how
-</t>
+          <t>how</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
